--- a/data/raw/Données+RH.xlsx
+++ b/data/raw/Données+RH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projets\p12_gerer_projet_infra\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D3E20C-59DE-46EF-A422-8B5A89DBFCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640AB2A5-C4D5-499B-ABE5-AF572FEBBC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
